--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104563_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104563_W12.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6115</v>
+        <v>4.6272</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2309</v>
+        <v>1.248</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3806</v>
+        <v>3.3792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5246</v>
+        <v>0.5219</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3764</v>
+        <v>-0.3871</v>
       </c>
       <c r="I2" t="n">
-        <v>0.901</v>
+        <v>0.909</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3001</v>
+        <v>-0.3262</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3748</v>
+        <v>-0.4007</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8247</v>
+        <v>0.8481</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5387</v>
+        <v>-0.4378</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2511</v>
+        <v>-0.6926</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2876</v>
+        <v>0.2548</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5212</v>
+        <v>3.1228</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4519</v>
+        <v>1.1545</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0693</v>
+        <v>1.9683</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0013</v>
+        <v>0.0056</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4891</v>
+        <v>0.491</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6163</v>
+        <v>0.6065</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4027</v>
+        <v>1.3962</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6176</v>
+        <v>-0.6009</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3883</v>
+        <v>-0.021</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2571</v>
+        <v>-0.5415</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6454</v>
+        <v>0.5206</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7796</v>
+        <v>1.2735</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2202</v>
+        <v>-0.0575</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9998</v>
+        <v>1.331</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3958</v>
+        <v>0.3965</v>
       </c>
       <c r="H4" t="n">
         <v>0.3131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0835</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0525</v>
+        <v>-0.0644</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4483</v>
+        <v>0.4609</v>
       </c>
       <c r="N4" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0283</v>
+        <v>-0.5296</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7652</v>
+        <v>-0.5786</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2631</v>
+        <v>0.049</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
@@ -799,22 +799,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1086</v>
+        <v>0.2102</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1781</v>
+        <v>0.2102</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0487</v>
+        <v>0.0523</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0696</v>
+        <v>0.0644</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1078</v>
+        <v>-2.6746</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0382</v>
+        <v>2.739</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.7346</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2234</v>
+        <v>0.2376</v>
       </c>
       <c r="I6" t="n">
-        <v>0.509</v>
+        <v>0.497</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9177</v>
+        <v>0.889</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7446</v>
+        <v>0.7412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1731</v>
+        <v>0.1478</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1852</v>
+        <v>-0.1544</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O6" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0638</v>
+        <v>0.1917</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5303</v>
+        <v>-1.0597</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5942</v>
+        <v>1.2514</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8449</v>
+        <v>-0.2835</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5768</v>
+        <v>-2.5535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7319</v>
+        <v>2.2699</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.706</v>
+        <v>-1.9678</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2612</v>
+        <v>-0.0983</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9672</v>
+        <v>-1.8695</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5252</v>
+        <v>-2.1421</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7966</v>
+        <v>0.1896</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1808</v>
+        <v>0.1743</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5354</v>
+        <v>-0.2879</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>0.4622</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3242</v>
+        <v>0.2486</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5565</v>
+        <v>-0.4114</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2323</v>
+        <v>0.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.639</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8515</v>
+        <v>-0.6747</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2756</v>
+        <v>-1.4819</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4241</v>
+        <v>0.8073</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.778</v>
+        <v>-1.7096</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3435</v>
+        <v>0.2613</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4345</v>
+        <v>-1.9709</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3813</v>
+        <v>-1.5388</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.7929</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4159</v>
+        <v>-2.3317</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3967</v>
+        <v>-0.1708</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3781</v>
+        <v>-0.5315</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0186</v>
+        <v>0.3608</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4857</v>
+        <v>-0.144</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>-0.4392</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1403</v>
+        <v>0.2951</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9771</v>
+        <v>-0.8639</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.966</v>
+        <v>-1.1757</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9889</v>
+        <v>0.3118</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9784</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1099</v>
+        <v>-0.3391</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8685</v>
+        <v>-0.4365</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1313</v>
+        <v>-0.3905</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1905</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.3218</v>
+        <v>-0.4249</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1529</v>
+        <v>-0.3852</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3003</v>
+        <v>-0.3736</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4532</v>
+        <v>-0.0116</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4258</v>
+        <v>-0.4947</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8347</v>
+        <v>-0.5089</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4089</v>
+        <v>0.0141</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3931</v>
+        <v>-1.4618</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5875</v>
+        <v>-1.8322</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1943</v>
+        <v>0.3704</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3266</v>
+        <v>0.6193</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1613</v>
+        <v>0.4677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4878</v>
+        <v>0.1516</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8686</v>
+        <v>-0.5298</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4608</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4078</v>
+        <v>-0.5816</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.542</v>
+        <v>1.1492</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6221</v>
+        <v>0.416</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08</v>
+        <v>0.7331</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2683</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.5367</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.163</v>
+        <v>-0.6957</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4657</v>
+        <v>-0.4114</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6288</v>
+        <v>-0.2843</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>-0.7025</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5463</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0338</v>
+        <v>-1.7395</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1619</v>
+        <v>-2.9999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.128</v>
+        <v>1.2604</v>
       </c>
       <c r="G11" t="n">
-        <v>0.62</v>
+        <v>0.3091</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4602</v>
+        <v>-0.1826</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1599</v>
+        <v>0.4917</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5159</v>
+        <v>1.8284</v>
       </c>
       <c r="K11" t="n">
-        <v>0.052</v>
+        <v>1.4264</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5679</v>
+        <v>0.4019</v>
       </c>
       <c r="M11" t="n">
-        <v>1.136</v>
+        <v>-1.5193</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4082</v>
+        <v>-1.6091</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7277</v>
+        <v>0.0898</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5878</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2663</v>
+        <v>-0.1593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.8204</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5012</v>
+        <v>0.6611</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7071</v>
+        <v>0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7071</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4141</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5184</v>
+        <v>-3.2281</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9008</v>
+        <v>-3.4943</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6176</v>
+        <v>0.2662</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5908</v>
+        <v>-1.6521</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1772</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5865</v>
+        <v>-1.5626</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.205</v>
+        <v>-2.3001</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2796</v>
+        <v>-0.1174</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0746</v>
+        <v>-2.1827</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3858</v>
+        <v>0.6481</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8976</v>
+        <v>0.028</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5118</v>
+        <v>0.6201</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3011</v>
+        <v>-0.2589</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1603</v>
+        <v>-0.6902</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1408</v>
+        <v>0.4313</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.5068</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6839</v>
+        <v>-4.0585</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8221</v>
+        <v>-3.0969</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1382</v>
+        <v>-0.9616</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6588</v>
+        <v>-2.5943</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0968</v>
+        <v>-3.1874</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.562</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2835</v>
+        <v>-2.2223</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.111</v>
+        <v>-2.2967</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1725</v>
+        <v>0.0745</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6247</v>
+        <v>-0.372</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0142</v>
+        <v>-0.8907</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6105</v>
+        <v>0.5187</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7056</v>
+        <v>0.7619</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0434</v>
+        <v>-0.0049</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3378</v>
+        <v>0.7667</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.351400000000001</v>
+        <v>-3.011899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.0055</v>
+        <v>-16.964</v>
       </c>
       <c r="F14" t="n">
-        <v>13.6538</v>
+        <v>13.9521</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.956600000000001</v>
+        <v>-5.9546</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5181</v>
+        <v>-2.5132</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4385</v>
+        <v>-3.440999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.9922</v>
+        <v>-6.190300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.978599999999999</v>
+        <v>1.8727</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.9709</v>
+        <v>-8.062899999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.03579999999999983</v>
+        <v>0.2358999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.4965</v>
+        <v>-4.386</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5321</v>
+        <v>4.621799999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0125</v>
+        <v>-17.0722</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8297</v>
+        <v>-1.4865</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.5024</v>
+        <v>-6.1588</v>
       </c>
       <c r="U14" t="n">
-        <v>4.672700000000001</v>
+        <v>4.6721</v>
       </c>
       <c r="V14" t="n">
-        <v>4.434800000000001</v>
+        <v>4.4293</v>
       </c>
       <c r="W14" t="n">
-        <v>12.5016</v>
+        <v>12.4575</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.066600000000001</v>
+        <v>-8.0282</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.478</v>
+        <v>5.5173</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7818</v>
+        <v>1.4524</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6962</v>
+        <v>4.0649</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9128</v>
+        <v>1.9064</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1126</v>
+        <v>2.1029</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1999</v>
+        <v>-0.1965</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5209</v>
+        <v>0.4979</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2326</v>
+        <v>1.2131</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3919</v>
+        <v>1.4085</v>
       </c>
       <c r="N15" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1531</v>
+        <v>1.2043</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6635</v>
+        <v>0.369</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4896</v>
+        <v>0.8353</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1617</v>
+        <v>3.9653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4146</v>
+        <v>0.3932</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7471</v>
+        <v>3.572</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0475</v>
+        <v>5.0605</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3317</v>
+        <v>1.3408</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7158</v>
+        <v>3.7197</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1487</v>
+        <v>3.1346</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9871</v>
+        <v>0.9825</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1617</v>
+        <v>2.1521</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8988</v>
+        <v>1.9259</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5541</v>
+        <v>1.5677</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2996</v>
+        <v>1.0837</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2389</v>
+        <v>-0.2374</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5385</v>
+        <v>1.3211</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6986</v>
+        <v>2.8832</v>
       </c>
       <c r="E17" t="n">
-        <v>2.641</v>
+        <v>0.5888</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0577</v>
+        <v>2.2944</v>
       </c>
       <c r="G17" t="n">
-        <v>2.519</v>
+        <v>0.4164</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6998</v>
+        <v>0.103</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1808</v>
+        <v>0.3134</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7721</v>
+        <v>0.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3075</v>
+        <v>0.8791</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5354</v>
+        <v>-0.679</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7469</v>
+        <v>0.2164</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3923</v>
+        <v>-0.7761</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3546</v>
+        <v>0.9925</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1647</v>
+        <v>-0.4147</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2299</v>
+        <v>-0.8993</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9348</v>
+        <v>0.4846</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3461</v>
+        <v>2.8814</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>2.8814</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.647</v>
+        <v>2.3233</v>
       </c>
       <c r="E18" t="n">
-        <v>0.285</v>
+        <v>2.2611</v>
       </c>
       <c r="F18" t="n">
-        <v>2.362</v>
+        <v>0.0623</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4281</v>
+        <v>2.5125</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0951</v>
+        <v>3.6938</v>
       </c>
       <c r="I18" t="n">
-        <v>0.333</v>
+        <v>-1.1813</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2325</v>
+        <v>1.7502</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8832</v>
+        <v>3.2922</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6506</v>
+        <v>-1.542</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1956</v>
+        <v>0.7623</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.788</v>
+        <v>0.4016</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9837</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6735</v>
+        <v>0.7817</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2521</v>
+        <v>-0.1233</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5786</v>
+        <v>0.905</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8924</v>
+        <v>-2.3367</v>
       </c>
       <c r="W18" t="n">
-        <v>2.8924</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5269</v>
+        <v>1.8071</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9685</v>
+        <v>-0.7804</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4954</v>
+        <v>2.5875</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4934</v>
+        <v>0.4816</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0349</v>
+        <v>0.0181</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4585</v>
+        <v>0.4635</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5094</v>
+        <v>-0.5401</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3574</v>
+        <v>-0.3834</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0028</v>
+        <v>1.0217</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3018</v>
+        <v>0.6017</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4688</v>
+        <v>-0.2325</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7706</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2519</v>
+        <v>0.3132</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6505</v>
+        <v>-1.5506</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9024</v>
+        <v>1.8638</v>
       </c>
       <c r="G20" t="n">
-        <v>0.242</v>
+        <v>0.2377</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6365</v>
+        <v>0.6294</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8671</v>
+        <v>-0.8838</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1091</v>
+        <v>1.1215</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7546</v>
+        <v>0.7608</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5148</v>
+        <v>0.5715</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0712</v>
+        <v>1.0107</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7429</v>
+        <v>-2.3755</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.023</v>
+        <v>-3.9335</v>
       </c>
       <c r="F21" t="n">
-        <v>1.28</v>
+        <v>1.558</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.764</v>
+        <v>-1.7597</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1963</v>
+        <v>-1.1921</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5678</v>
+        <v>-0.5675</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5706</v>
+        <v>-1.5892</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1935</v>
+        <v>-0.1704</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1396</v>
+        <v>-0.7736</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0253</v>
+        <v>-0.9086</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1143</v>
+        <v>0.135</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.188</v>
+        <v>-2.9723</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9225</v>
+        <v>-3.8306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.8583</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8121</v>
+        <v>-1.808</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0577</v>
+        <v>-1.0542</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7543</v>
+        <v>-0.7537</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2186</v>
+        <v>-1.2375</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1283</v>
+        <v>-0.1346</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5935</v>
+        <v>-0.5704</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O22" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9657</v>
+        <v>-0.7561</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2521</v>
+        <v>-1.1362</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2864</v>
+        <v>0.3801</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0612</v>
+        <v>-3.8848</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8563</v>
+        <v>-3.638</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.205</v>
+        <v>-0.2467</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5447</v>
+        <v>-0.5405</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6002</v>
+        <v>-1.5998</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0556</v>
+        <v>1.0593</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8893</v>
+        <v>-0.8988</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0013</v>
+        <v>-1.0105</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4258</v>
+        <v>-0.2532</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>-0.3719</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4102</v>
+        <v>-2.4082</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4205</v>
+        <v>-4.2166</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3557</v>
+        <v>-4.9145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9352</v>
+        <v>0.6979</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5654</v>
+        <v>-0.5527</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5383</v>
+        <v>-1.5285</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9729</v>
+        <v>0.9758</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.6692</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0893</v>
+        <v>0.1165</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2396</v>
+        <v>1.2518</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3995</v>
+        <v>-0.2102</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1644</v>
+        <v>-0.6926</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7649</v>
+        <v>0.4824</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.351499999999998</v>
+        <v>3.360199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.6541</v>
+        <v>-13.9521</v>
       </c>
       <c r="F25" t="n">
-        <v>17.0054</v>
+        <v>17.3124</v>
       </c>
       <c r="G25" t="n">
-        <v>5.956600000000001</v>
+        <v>5.954200000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5181</v>
+        <v>2.5134</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4385</v>
+        <v>3.4411</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0355000000000002</v>
+        <v>-0.2359000000000004</v>
       </c>
       <c r="K25" t="n">
-        <v>4.496699999999999</v>
+        <v>4.385999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.532</v>
+        <v>-4.6217</v>
       </c>
       <c r="M25" t="n">
-        <v>5.991999999999999</v>
+        <v>6.190300000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.9787</v>
+        <v>-1.8725</v>
       </c>
       <c r="O25" t="n">
-        <v>7.970800000000001</v>
+        <v>8.063099999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S25" t="n">
-        <v>1.829900000000001</v>
+        <v>1.8351</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.672600000000001</v>
+        <v>-4.672</v>
       </c>
       <c r="U25" t="n">
-        <v>6.5024</v>
+        <v>6.5071</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.434900000000001</v>
+        <v>-4.4294</v>
       </c>
       <c r="W25" t="n">
-        <v>8.066699999999999</v>
+        <v>8.0282</v>
       </c>
       <c r="X25" t="n">
-        <v>-12.5014</v>
+        <v>-12.4574</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104563_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104563_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.0282</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104563_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-12.4574</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
